--- a/Data/RemapDrafts/FischlRemapDraft.xlsx
+++ b/Data/RemapDrafts/FischlRemapDraft.xlsx
@@ -1,24 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Computer\Games\Genshin\Repos\Repos\Fix-Raiden-Boss\Data\RemapDrafts\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1B4CF3F-52E4-4BBA-9B9D-6BF4EF514075}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73DA0A65-6915-4C48-B7EB-1E67DEF5559A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="15720" xr2:uid="{B8774079-06D1-4EC7-AB7E-423E5EF7D19C}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="34620" windowHeight="13900" activeTab="1" xr2:uid="{B8774079-06D1-4EC7-AB7E-423E5EF7D19C}"/>
   </bookViews>
   <sheets>
-    <sheet name="V4.0 -Fischl to FischlHighness" sheetId="1" r:id="rId1"/>
-    <sheet name="V4.0 - FischlHighness to Fischl" sheetId="2" r:id="rId2"/>
+    <sheet name="Credits" sheetId="3" r:id="rId1"/>
+    <sheet name="V4.0 -Fischl to FischlHighness" sheetId="1" r:id="rId2"/>
+    <sheet name="V4.0 - FischlHighness to Fischl" sheetId="2" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 - FischlHighness to Fischl'!$A$1:$D$93</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'V4.0 -Fischl to FischlHighness'!$A$1:$D$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'V4.0 - FischlHighness to Fischl'!$A$1:$D$93</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'V4.0 -Fischl to FischlHighness'!$A$1:$D$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -41,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="26">
   <si>
     <t>Uncertainty</t>
   </si>
@@ -110,13 +111,22 @@
   </si>
   <si>
     <t>FischlHighness' back ribbon, bottom part</t>
+  </si>
+  <si>
+    <t>Authors</t>
+  </si>
+  <si>
+    <t>Name</t>
+  </si>
+  <si>
+    <t>AlbertGold#2696</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -127,6 +137,22 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="20"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
@@ -150,14 +176,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="2">
@@ -510,17 +540,48 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{354BFAB1-94B5-4331-8EBF-B42F1F31029F}">
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="14.453125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="26" x14ac:dyDescent="0.6">
+      <c r="A1" s="2" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+      <c r="A4" s="3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="A4" r:id="rId1" xr:uid="{D057B658-EA1E-45AA-928B-244F77172840}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{55CFD5C0-3F2C-4081-9F85-C2568404EB79}">
   <dimension ref="A1:D96"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="10.140625" customWidth="1"/>
-    <col min="2" max="2" width="20.28515625" customWidth="1"/>
+    <col min="1" max="1" width="10.1796875" customWidth="1"/>
+    <col min="2" max="2" width="20.26953125" customWidth="1"/>
     <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="91.28515625" customWidth="1"/>
+    <col min="4" max="4" width="91.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>2</v>
       </c>
@@ -534,7 +595,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -548,7 +609,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -556,7 +617,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -564,7 +625,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -572,7 +633,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -580,7 +641,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -588,7 +649,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -596,7 +657,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -604,7 +665,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -612,7 +673,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -620,7 +681,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -628,7 +689,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -639,7 +700,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -647,7 +708,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -655,7 +716,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -666,7 +727,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -674,7 +735,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -682,7 +743,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -690,7 +751,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -698,7 +759,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -709,7 +770,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -720,7 +781,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -728,7 +789,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -736,7 +797,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -744,7 +805,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -752,7 +813,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -763,7 +824,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -771,7 +832,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -779,7 +840,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -787,7 +848,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -795,7 +856,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -806,7 +867,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -814,7 +875,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -828,7 +889,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -839,7 +900,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -850,7 +911,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -858,7 +919,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -872,7 +933,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -883,7 +944,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -894,7 +955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -902,7 +963,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -913,7 +974,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -921,7 +982,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -932,7 +993,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -943,7 +1004,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -954,7 +1015,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -965,7 +1026,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -973,7 +1034,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -981,7 +1042,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -992,7 +1053,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1000,7 +1061,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1008,7 +1069,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1016,7 +1077,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1024,7 +1085,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1032,7 +1093,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1040,7 +1101,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1048,7 +1109,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1056,7 +1117,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1064,7 +1125,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1072,7 +1133,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1080,7 +1141,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1088,7 +1149,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1096,7 +1157,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1104,7 +1165,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1112,7 +1173,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1120,7 +1181,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1128,7 +1189,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1136,7 +1197,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1144,7 +1205,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1152,7 +1213,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1160,7 +1221,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1168,7 +1229,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1176,7 +1237,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1184,7 +1245,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1192,7 +1253,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -1200,7 +1261,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -1208,7 +1269,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -1216,7 +1277,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -1224,7 +1285,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -1232,7 +1293,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -1240,7 +1301,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -1248,7 +1309,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -1256,7 +1317,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -1264,7 +1325,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -1272,7 +1333,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -1280,7 +1341,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -1288,7 +1349,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -1296,7 +1357,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -1304,7 +1365,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -1312,7 +1373,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
@@ -1320,7 +1381,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92">
         <v>90</v>
       </c>
@@ -1328,7 +1389,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93">
         <v>91</v>
       </c>
@@ -1336,7 +1397,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94">
         <v>92</v>
       </c>
@@ -1344,7 +1405,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95">
         <v>93</v>
       </c>
@@ -1352,7 +1413,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96">
         <v>94</v>
       </c>
@@ -1370,17 +1431,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D4A52C9-4021-4692-804B-E7F7D958903D}">
   <dimension ref="A1:D91"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="14.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-    <col min="4" max="4" width="84.85546875" customWidth="1"/>
+    <col min="1" max="2" width="14.81640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.54296875" customWidth="1"/>
+    <col min="4" max="4" width="84.81640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>3</v>
       </c>
@@ -1394,7 +1455,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
@@ -1402,7 +1463,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1410,7 +1471,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1424,7 +1485,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1432,7 +1493,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>4</v>
       </c>
@@ -1440,7 +1501,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>5</v>
       </c>
@@ -1448,7 +1509,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>6</v>
       </c>
@@ -1456,7 +1517,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>7</v>
       </c>
@@ -1464,7 +1525,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>8</v>
       </c>
@@ -1472,7 +1533,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>9</v>
       </c>
@@ -1480,7 +1541,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>10</v>
       </c>
@@ -1488,7 +1549,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>11</v>
       </c>
@@ -1496,7 +1557,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14">
         <v>12</v>
       </c>
@@ -1504,7 +1565,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15">
         <v>13</v>
       </c>
@@ -1512,7 +1573,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16">
         <v>14</v>
       </c>
@@ -1520,7 +1581,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17">
         <v>15</v>
       </c>
@@ -1528,7 +1589,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18">
         <v>16</v>
       </c>
@@ -1536,7 +1597,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19">
         <v>17</v>
       </c>
@@ -1544,7 +1605,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20">
         <v>18</v>
       </c>
@@ -1558,7 +1619,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21">
         <v>19</v>
       </c>
@@ -1566,7 +1627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A22">
         <v>20</v>
       </c>
@@ -1574,7 +1635,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23">
         <v>21</v>
       </c>
@@ -1582,7 +1643,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24">
         <v>22</v>
       </c>
@@ -1590,7 +1651,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A25">
         <v>23</v>
       </c>
@@ -1598,7 +1659,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A26">
         <v>24</v>
       </c>
@@ -1606,7 +1667,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A27">
         <v>25</v>
       </c>
@@ -1614,7 +1675,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A28">
         <v>26</v>
       </c>
@@ -1622,7 +1683,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A29">
         <v>27</v>
       </c>
@@ -1630,7 +1691,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A30">
         <v>28</v>
       </c>
@@ -1638,7 +1699,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A31">
         <v>29</v>
       </c>
@@ -1646,7 +1707,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A32">
         <v>30</v>
       </c>
@@ -1654,7 +1715,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33">
         <v>31</v>
       </c>
@@ -1662,7 +1723,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34">
         <v>32</v>
       </c>
@@ -1670,7 +1731,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35">
         <v>33</v>
       </c>
@@ -1678,7 +1739,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36">
         <v>34</v>
       </c>
@@ -1686,7 +1747,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37">
         <v>35</v>
       </c>
@@ -1694,7 +1755,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38">
         <v>36</v>
       </c>
@@ -1702,7 +1763,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39">
         <v>37</v>
       </c>
@@ -1710,7 +1771,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40">
         <v>38</v>
       </c>
@@ -1718,7 +1779,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41">
         <v>39</v>
       </c>
@@ -1726,7 +1787,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42">
         <v>40</v>
       </c>
@@ -1734,7 +1795,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43">
         <v>41</v>
       </c>
@@ -1742,7 +1803,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44">
         <v>42</v>
       </c>
@@ -1750,7 +1811,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45">
         <v>43</v>
       </c>
@@ -1758,7 +1819,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46">
         <v>44</v>
       </c>
@@ -1766,7 +1827,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47">
         <v>45</v>
       </c>
@@ -1774,7 +1835,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48">
         <v>46</v>
       </c>
@@ -1782,7 +1843,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49">
         <v>47</v>
       </c>
@@ -1790,7 +1851,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50">
         <v>48</v>
       </c>
@@ -1798,7 +1859,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51">
         <v>49</v>
       </c>
@@ -1806,7 +1867,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52">
         <v>50</v>
       </c>
@@ -1814,7 +1875,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53">
         <v>51</v>
       </c>
@@ -1822,7 +1883,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54">
         <v>52</v>
       </c>
@@ -1830,7 +1891,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55">
         <v>53</v>
       </c>
@@ -1838,7 +1899,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56">
         <v>54</v>
       </c>
@@ -1846,7 +1907,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57">
         <v>55</v>
       </c>
@@ -1854,7 +1915,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58">
         <v>56</v>
       </c>
@@ -1862,7 +1923,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59">
         <v>57</v>
       </c>
@@ -1870,7 +1931,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60">
         <v>58</v>
       </c>
@@ -1878,7 +1939,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61">
         <v>59</v>
       </c>
@@ -1886,7 +1947,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62">
         <v>60</v>
       </c>
@@ -1894,7 +1955,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63">
         <v>61</v>
       </c>
@@ -1902,7 +1963,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64">
         <v>62</v>
       </c>
@@ -1910,7 +1971,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65">
         <v>63</v>
       </c>
@@ -1918,7 +1979,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66">
         <v>64</v>
       </c>
@@ -1926,7 +1987,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67">
         <v>65</v>
       </c>
@@ -1934,7 +1995,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68">
         <v>66</v>
       </c>
@@ -1942,7 +2003,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69">
         <v>67</v>
       </c>
@@ -1950,7 +2011,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70">
         <v>68</v>
       </c>
@@ -1958,7 +2019,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71">
         <v>69</v>
       </c>
@@ -1966,7 +2027,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72">
         <v>70</v>
       </c>
@@ -1974,7 +2035,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73">
         <v>71</v>
       </c>
@@ -1982,7 +2043,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74">
         <v>72</v>
       </c>
@@ -1990,7 +2051,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75">
         <v>73</v>
       </c>
@@ -1998,7 +2059,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76">
         <v>74</v>
       </c>
@@ -2006,7 +2067,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77">
         <v>75</v>
       </c>
@@ -2014,7 +2075,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78">
         <v>76</v>
       </c>
@@ -2022,7 +2083,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79">
         <v>77</v>
       </c>
@@ -2030,7 +2091,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80">
         <v>78</v>
       </c>
@@ -2038,7 +2099,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81">
         <v>79</v>
       </c>
@@ -2046,7 +2107,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82">
         <v>80</v>
       </c>
@@ -2054,7 +2115,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83">
         <v>81</v>
       </c>
@@ -2062,7 +2123,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84">
         <v>82</v>
       </c>
@@ -2070,7 +2131,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85">
         <v>83</v>
       </c>
@@ -2078,7 +2139,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86">
         <v>84</v>
       </c>
@@ -2086,7 +2147,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87">
         <v>85</v>
       </c>
@@ -2094,7 +2155,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88">
         <v>86</v>
       </c>
@@ -2102,7 +2163,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89">
         <v>87</v>
       </c>
@@ -2110,7 +2171,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90">
         <v>88</v>
       </c>
@@ -2118,7 +2179,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91">
         <v>89</v>
       </c>
